--- a/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
+++ b/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
@@ -547,16 +547,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -619,6 +619,11 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
+          <t>Unmapped</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>Excluded</t>
         </is>
       </c>
@@ -650,6 +655,9 @@
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -678,6 +686,9 @@
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -706,6 +717,9 @@
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -732,6 +746,9 @@
         <v>28</v>
       </c>
       <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -760,6 +777,9 @@
         <v>29</v>
       </c>
       <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -790,6 +810,9 @@
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -818,6 +841,9 @@
       <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -846,6 +872,9 @@
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -868,6 +897,9 @@
         <v>241</v>
       </c>
       <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2524,7 +2556,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Only 'New' notes appear. Each block is one Bulk Generate run: set the Subject and Domain Context shown, paste the titles as topics.</t>
+          <t>Only 'New' and 'Unmapped' notes appear. Each block is one Bulk Generate run: set the Subject and Domain Context shown, paste the titles as topics.</t>
         </is>
       </c>
     </row>

--- a/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
+++ b/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Domain Context" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1 History and Theory of Archite" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2 Architectural Design" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3 Planning and Site Development" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4 Building Materials and Constr" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5 Structural Concepts for Archi" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="6 Building Utilities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="7 Building Laws and Regulations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="8 Architectural Practice" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="By Subject (bulk generate)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Context" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 History and Theory of Archite" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Architectural Design" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Planning and Site Development" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Building Materials and Constr" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Structural Concepts for Archi" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Building Utilities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Building Laws and Regulations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Architectural Practice" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Subject (bulk generate)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,6 +182,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7577,12 +7578,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7613,6 +7615,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -7629,6 +7632,11 @@
           <t>Notes in set</t>
         </is>
       </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -7644,6 +7652,11 @@
       <c r="C7" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Interior Design, MS Heritage Conservation, MS Historic Preservation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7659,6 +7672,11 @@
       <c r="C8" s="5" t="n">
         <v>57</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Interior Design, BS Architectural Engineering, BS Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -7674,6 +7692,11 @@
       <c r="C9" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Interior Design, BS Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -7689,6 +7712,11 @@
       <c r="C10" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Interior Design, BS Environmental Planning, BS Real Estate Management</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -7704,6 +7732,11 @@
       <c r="C11" s="5" t="n">
         <v>31</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Architectural Engineering, BS Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -7719,6 +7752,11 @@
       <c r="C12" s="5" t="n">
         <v>41</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Architectural Engineering, BS Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7734,6 +7772,11 @@
       <c r="C13" s="5" t="n">
         <v>6</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Construction Management, BS Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7749,6 +7792,11 @@
       <c r="C14" s="5" t="n">
         <v>2</v>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Construction Management, BS Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -7764,6 +7812,11 @@
       <c r="C15" s="5" t="n">
         <v>12</v>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -7779,6 +7832,11 @@
       <c r="C16" s="5" t="n">
         <v>6</v>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Construction Management, BS Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -7794,6 +7852,11 @@
       <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Interior Design, BS Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -7809,6 +7872,11 @@
       <c r="C18" s="5" t="n">
         <v>16</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BS Civil Engineering, BS Architecture, BS Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -7824,6 +7892,11 @@
       <c r="C19" s="5" t="n">
         <v>33</v>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Interior Design, BS Landscape Architecture, Fine Arts / Art History</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -7839,6 +7912,11 @@
       <c r="C20" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Landscape Architecture, BS Urban &amp; Regional Planning, BS Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -7854,6 +7932,11 @@
       <c r="C21" s="5" t="n">
         <v>21</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Interior Design, BS Environmental Planning, BS Real Estate Management</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -7869,6 +7952,11 @@
       <c r="C22" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Interior Design, BS Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -7884,6 +7972,11 @@
       <c r="C23" s="5" t="n">
         <v>39</v>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Interior Design, BS Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -7899,6 +7992,11 @@
       <c r="C24" s="5" t="n">
         <v>4</v>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Construction Management, BS Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -7914,6 +8012,11 @@
       <c r="C25" s="5" t="n">
         <v>20</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Landscape Architecture, BS Urban &amp; Regional Planning, BS Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -7929,6 +8032,11 @@
       <c r="C26" s="5" t="n">
         <v>32</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Civil Engineering, BS Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -7944,6 +8052,11 @@
       <c r="C27" s="5" t="n">
         <v>11</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Interior Design, BS Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -7958,6 +8071,11 @@
       </c>
       <c r="C28" s="5" t="n">
         <v>14</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BS Architecture, BS Landscape Architecture, BS Urban &amp; Regional Planning, BS Environmental Planning</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
+++ b/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
@@ -566,14 +566,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️ ALE Comprehensive Review — target shape — target shape</t>
+          <t>🏛️ ALE Comprehensive Review — target shape</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepare for the Philippine Architect Licensure Examination through comprehensive review of architectural history and theory, design, planning and site development, building materials and construction, structural concepts, building utilities, laws and regulations, and professional practice.</t>
+          <t>Prepare for the Philippine Architect Licensure Examination through comprehensive review of architectural history and theory, professional practice, planning, structural concepts, building technology, utilities, architectural design, and site planning.</t>
         </is>
       </c>
     </row>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Parking Requirements in Architectural Design and Urban Planning</t>
+          <t>Parking Requirements under the National Building Code</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Stairway Design Standards in Architecture</t>
+          <t>Stairway Design Standards under the National Building Code</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Accessibility Requirements in Architectural Design</t>
+          <t>Accessibility Requirements under BP 344</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Ramp Slope Standards in Architectural Design</t>
+          <t>Ramp Slope Standards under BP 344</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Design Principles and Standards for Accessible Toilets in Architecture</t>
+          <t>Accessible Toilet Design Standards under BP 344</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Parking Requirements for Persons with Disabilities in Architectural Design</t>
+          <t>Accessible Parking Requirements under BP 344</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">

--- a/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
+++ b/docs/curriculum/ale-comprehensive-review-target-shape.xlsx
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -931,6 +931,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -983,6 +984,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1016,6 +1022,11 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
         </is>
       </c>
     </row>
@@ -1045,6 +1056,11 @@
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -1072,6 +1088,11 @@
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -1099,6 +1120,11 @@
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -1126,6 +1152,11 @@
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -1153,6 +1184,11 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1184,6 +1220,11 @@
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -1211,6 +1252,11 @@
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -1238,6 +1284,11 @@
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -1265,6 +1316,11 @@
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -1292,6 +1348,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -1319,6 +1380,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1350,6 +1416,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -1377,6 +1448,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -1404,6 +1480,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -1431,6 +1512,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -1458,6 +1544,11 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
@@ -1485,6 +1576,11 @@
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -1512,6 +1608,11 @@
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1543,6 +1644,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -1570,6 +1676,11 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -1597,6 +1708,11 @@
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -1624,6 +1740,11 @@
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1655,6 +1776,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -1682,6 +1808,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -1709,6 +1840,11 @@
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr"/>
@@ -1736,6 +1872,11 @@
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -1763,6 +1904,11 @@
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1796,6 +1942,11 @@
       <c r="G38" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
         </is>
       </c>
     </row>
@@ -1829,6 +1980,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
@@ -1860,6 +2016,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr"/>
@@ -1891,6 +2052,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -1922,6 +2088,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -1953,6 +2124,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
@@ -1980,6 +2156,11 @@
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr"/>
@@ -2007,6 +2188,11 @@
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
@@ -2034,6 +2220,11 @@
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -2061,6 +2252,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -2088,6 +2284,11 @@
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -2115,6 +2316,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
@@ -2142,6 +2348,11 @@
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -2175,6 +2386,11 @@
       <c r="G52" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
         </is>
       </c>
     </row>
@@ -2208,6 +2424,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
@@ -2239,6 +2460,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -2270,6 +2496,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -2301,6 +2532,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -2332,6 +2568,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -2365,6 +2606,11 @@
       <c r="G59" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
         </is>
       </c>
     </row>
@@ -2398,6 +2644,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr"/>
@@ -2429,6 +2680,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr"/>
@@ -2460,6 +2716,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr"/>
@@ -2491,6 +2752,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr"/>
@@ -2520,6 +2786,11 @@
       <c r="G64" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F261"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2547,6 +2818,7 @@
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2594,6 +2866,11 @@
           <t>Note title</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2622,6 +2899,11 @@
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Anthropometrics in Architectural Design</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -2644,6 +2926,11 @@
           <t>Ergonomics in Architectural Design</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -2664,6 +2951,11 @@
           <t>Architectural Problem Analysis</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -2684,6 +2976,11 @@
           <t>Architectural Programming Methods</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -2704,6 +3001,11 @@
           <t>User and Client Requirements Analysis</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -2724,6 +3026,11 @@
           <t>Functional Relationship Analysis</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -2744,6 +3051,11 @@
           <t>Adjacency and Bubble Diagrams</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -2764,6 +3076,11 @@
           <t>Design Concept Development</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -2784,6 +3101,11 @@
           <t>Architectural Design Methodology</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -2804,6 +3126,11 @@
           <t>Spatial Organization Systems</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -2824,6 +3151,11 @@
           <t>Horizontal Circulation</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -2844,6 +3176,11 @@
           <t>Vertical Circulation</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -2864,6 +3201,11 @@
           <t>Entrance and Access Planning</t>
         </is>
       </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
@@ -2884,6 +3226,11 @@
           <t>Service and Public Circulation</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -2904,6 +3251,11 @@
           <t>Space Efficiency and Building Planning</t>
         </is>
       </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -2924,6 +3276,11 @@
           <t>Single-Family Residential Planning</t>
         </is>
       </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -2944,6 +3301,11 @@
           <t>Multi-Family Residential Planning</t>
         </is>
       </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -2964,6 +3326,11 @@
           <t>Apartment and Condominium Planning</t>
         </is>
       </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -2984,6 +3351,11 @@
           <t>Socialized and Affordable Housing Design</t>
         </is>
       </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
@@ -3004,6 +3376,11 @@
           <t>Housing for Special User Groups</t>
         </is>
       </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -3024,6 +3401,11 @@
           <t>Residential Subdivision Planning</t>
         </is>
       </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
@@ -3044,6 +3426,11 @@
           <t>Office Building Planning</t>
         </is>
       </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -3064,6 +3451,11 @@
           <t>Retail and Commercial Building Planning</t>
         </is>
       </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -3084,6 +3476,11 @@
           <t>Market Planning and Design</t>
         </is>
       </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -3104,6 +3501,11 @@
           <t>Hotel and Hospitality Planning</t>
         </is>
       </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -3124,6 +3526,11 @@
           <t>Mixed-Use Building Planning</t>
         </is>
       </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr"/>
@@ -3144,6 +3551,11 @@
           <t>School and Educational Facility Planning</t>
         </is>
       </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
@@ -3164,6 +3576,11 @@
           <t>Library and Cultural Facility Planning</t>
         </is>
       </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -3184,6 +3601,11 @@
           <t>Hospital and Healthcare Facility Planning</t>
         </is>
       </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -3204,6 +3626,11 @@
           <t>Government Building Planning</t>
         </is>
       </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr"/>
@@ -3224,6 +3651,11 @@
           <t>Religious Building Planning</t>
         </is>
       </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -3244,6 +3676,11 @@
           <t>Sports Facility Planning</t>
         </is>
       </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
@@ -3264,6 +3701,11 @@
           <t>Theater and Auditorium Planning</t>
         </is>
       </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
@@ -3284,6 +3726,11 @@
           <t>Recreational Facility Planning</t>
         </is>
       </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
@@ -3304,6 +3751,11 @@
           <t>Parks and Open-Space Design</t>
         </is>
       </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
@@ -3324,6 +3776,11 @@
           <t>Industrial Building Planning</t>
         </is>
       </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr"/>
@@ -3344,6 +3801,11 @@
           <t>Agricultural Facility Planning</t>
         </is>
       </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -3364,6 +3826,11 @@
           <t>Transportation Terminal Planning</t>
         </is>
       </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -3384,6 +3851,11 @@
           <t>Airport Architectural Planning</t>
         </is>
       </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
@@ -3404,6 +3876,11 @@
           <t>Seaport and Port Facility Planning</t>
         </is>
       </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr"/>
@@ -3424,6 +3901,11 @@
           <t>Service and Utility Facility Planning</t>
         </is>
       </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
@@ -3444,6 +3926,11 @@
           <t>Mixed-Use Complex Planning</t>
         </is>
       </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -3464,6 +3951,11 @@
           <t>Multi-Building Site Planning</t>
         </is>
       </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -3484,6 +3976,11 @@
           <t>Campus and Institutional Complex Planning</t>
         </is>
       </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -3504,6 +4001,11 @@
           <t>Integrated Architectural Design Problems</t>
         </is>
       </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -3532,6 +4034,11 @@
       <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Architectural Specifications</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
         </is>
       </c>
     </row>
@@ -3554,6 +4061,11 @@
           <t>Construction Specifications Fundamentals</t>
         </is>
       </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr"/>
@@ -3574,6 +4086,11 @@
           <t>Construction Drawings and Details</t>
         </is>
       </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
@@ -3594,6 +4111,11 @@
           <t>Coordination of Architectural Construction Documents</t>
         </is>
       </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -3614,6 +4136,11 @@
           <t>Scope and Key Provisions of the Architecture Act of 2004</t>
         </is>
       </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -3634,6 +4161,11 @@
           <t>Registration and Licensure of Architects</t>
         </is>
       </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -3654,6 +4186,11 @@
           <t>Scope of Architectural Practice</t>
         </is>
       </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr"/>
@@ -3674,6 +4211,11 @@
           <t>Rights and Responsibilities of Architects</t>
         </is>
       </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr"/>
@@ -3694,6 +4236,11 @@
           <t>Professional Organization of Architects</t>
         </is>
       </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr"/>
@@ -3714,6 +4261,11 @@
           <t>Architect's Code of Ethical Conduct</t>
         </is>
       </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr"/>
@@ -3734,6 +4286,11 @@
           <t>Duties of Architects to the Public</t>
         </is>
       </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr"/>
@@ -3754,6 +4311,11 @@
           <t>Duties of Architects to Clients</t>
         </is>
       </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr"/>
@@ -3774,6 +4336,11 @@
           <t>Duties of Architects to Contractors</t>
         </is>
       </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr"/>
@@ -3794,6 +4361,11 @@
           <t>Duties of Architects to Colleagues and the Profession</t>
         </is>
       </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr"/>
@@ -3814,6 +4386,11 @@
           <t>Conflicts of Interest and Professional Integrity</t>
         </is>
       </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr"/>
@@ -3834,6 +4411,11 @@
           <t>Spectrum of Architectural Services</t>
         </is>
       </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr"/>
@@ -3854,6 +4436,11 @@
           <t>Regular Design Services</t>
         </is>
       </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr"/>
@@ -3874,6 +4461,11 @@
           <t>Pre-Design Services</t>
         </is>
       </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr"/>
@@ -3894,6 +4486,11 @@
           <t>Specialized Architectural Services</t>
         </is>
       </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr"/>
@@ -3914,6 +4511,11 @@
           <t>Construction-Related Architectural Services</t>
         </is>
       </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr"/>
@@ -3934,6 +4536,11 @@
           <t>Post-Construction Services</t>
         </is>
       </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr"/>
@@ -3954,6 +4561,11 @@
           <t>Comprehensive Architectural Services</t>
         </is>
       </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr"/>
@@ -3974,6 +4586,11 @@
           <t>Methods of Compensation for Architectural Services</t>
         </is>
       </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr"/>
@@ -3994,6 +4611,11 @@
           <t>Architectural Professional Fees</t>
         </is>
       </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr"/>
@@ -4014,6 +4636,11 @@
           <t>Owner-Architect Agreements</t>
         </is>
       </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr"/>
@@ -4034,6 +4661,11 @@
           <t>Scope Changes and Additional Services</t>
         </is>
       </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr"/>
@@ -4054,6 +4686,11 @@
           <t>Architectural Contract Documents</t>
         </is>
       </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr"/>
@@ -4074,6 +4711,11 @@
           <t>Plans, Specifications, and Schedules</t>
         </is>
       </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr"/>
@@ -4094,6 +4736,11 @@
           <t>Specifications Writing</t>
         </is>
       </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr"/>
@@ -4114,6 +4761,11 @@
           <t>General and Special Conditions of Construction Contracts</t>
         </is>
       </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr"/>
@@ -4134,6 +4786,11 @@
           <t>Addenda and Supplemental Documents</t>
         </is>
       </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Construction Management</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr"/>
@@ -4154,6 +4811,11 @@
           <t>Architect's Role During Construction</t>
         </is>
       </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr"/>
@@ -4174,6 +4836,11 @@
           <t>Submittals and Shop Drawings</t>
         </is>
       </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr"/>
@@ -4194,6 +4861,11 @@
           <t>Requests for Information During Construction</t>
         </is>
       </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr"/>
@@ -4214,6 +4886,11 @@
           <t>Change Orders</t>
         </is>
       </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr"/>
@@ -4234,6 +4911,11 @@
           <t>Progress Billing and Certification</t>
         </is>
       </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr"/>
@@ -4254,6 +4936,11 @@
           <t>Substantial and Final Completion</t>
         </is>
       </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr"/>
@@ -4274,6 +4961,11 @@
           <t>Punch Listing and Project Turnover</t>
         </is>
       </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -4302,6 +4994,11 @@
       <c r="F90" s="5" t="inlineStr">
         <is>
           <t>Building Water Supply Systems</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -4324,6 +5021,11 @@
           <t>Water Storage and Distribution in Buildings</t>
         </is>
       </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr"/>
@@ -4344,6 +5046,11 @@
           <t>Building Drainage Systems</t>
         </is>
       </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr"/>
@@ -4364,6 +5071,11 @@
           <t>Building Sewerage Systems</t>
         </is>
       </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr"/>
@@ -4384,6 +5096,11 @@
           <t>Stormwater Systems for Buildings</t>
         </is>
       </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr"/>
@@ -4404,6 +5121,11 @@
           <t>Waste Treatment and Recycling Systems in Buildings</t>
         </is>
       </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr"/>
@@ -4424,6 +5146,11 @@
           <t>Natural and Mechanical Ventilation</t>
         </is>
       </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr"/>
@@ -4444,6 +5171,11 @@
           <t>Air-Conditioning Systems</t>
         </is>
       </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr"/>
@@ -4464,6 +5196,11 @@
           <t>Heating Systems in Buildings</t>
         </is>
       </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr"/>
@@ -4484,6 +5221,11 @@
           <t>Elevators and Escalators</t>
         </is>
       </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr"/>
@@ -4504,6 +5246,11 @@
           <t>Building Mechanical Equipment</t>
         </is>
       </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr"/>
@@ -4524,6 +5271,11 @@
           <t>Electrical Service and Distribution in Buildings</t>
         </is>
       </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr"/>
@@ -4544,6 +5296,11 @@
           <t>Electrical Loads and Circuits for Buildings</t>
         </is>
       </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr"/>
@@ -4564,6 +5321,11 @@
           <t>Emergency and Standby Power Systems</t>
         </is>
       </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr"/>
@@ -4584,6 +5346,11 @@
           <t>Alternative Energy Systems for Buildings</t>
         </is>
       </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr"/>
@@ -4604,6 +5371,11 @@
           <t>Lighting Fundamentals</t>
         </is>
       </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr"/>
@@ -4624,6 +5396,11 @@
           <t>Daylighting Design</t>
         </is>
       </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr"/>
@@ -4644,6 +5421,11 @@
           <t>Sound Transmission in Buildings</t>
         </is>
       </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr"/>
@@ -4664,6 +5446,11 @@
           <t>Room Acoustics</t>
         </is>
       </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr"/>
@@ -4684,6 +5471,11 @@
           <t>Acoustic Treatment and Noise Control</t>
         </is>
       </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr"/>
@@ -4704,6 +5496,11 @@
           <t>Fire Detection and Alarm Systems</t>
         </is>
       </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr"/>
@@ -4724,6 +5521,11 @@
           <t>Automatic Sprinkler Systems</t>
         </is>
       </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr"/>
@@ -4744,6 +5546,11 @@
           <t>Standpipes and Fire Hose Systems</t>
         </is>
       </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr"/>
@@ -4764,6 +5571,11 @@
           <t>Smoke Control Systems</t>
         </is>
       </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr"/>
@@ -4784,6 +5596,11 @@
           <t>Fire Protection Equipment</t>
         </is>
       </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr"/>
@@ -4804,6 +5621,11 @@
           <t>Building Communication Systems</t>
         </is>
       </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr"/>
@@ -4824,6 +5646,11 @@
           <t>Data and Telecommunications Systems</t>
         </is>
       </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr"/>
@@ -4844,6 +5671,11 @@
           <t>Security and Access Control Systems</t>
         </is>
       </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr"/>
@@ -4864,6 +5696,11 @@
           <t>CCTV Systems</t>
         </is>
       </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr"/>
@@ -4884,6 +5721,11 @@
           <t>Building Management Systems</t>
         </is>
       </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr"/>
@@ -4904,6 +5746,11 @@
           <t>Intelligent Building Technologies</t>
         </is>
       </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -4932,6 +5779,11 @@
       <c r="F122" s="5" t="inlineStr">
         <is>
           <t>Forces and Equilibrium in Building Structures</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -4954,6 +5806,11 @@
           <t>Structural Loads and Load Paths</t>
         </is>
       </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr"/>
@@ -4974,6 +5831,11 @@
           <t>Structural Stability Fundamentals</t>
         </is>
       </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr"/>
@@ -4994,6 +5856,11 @@
           <t>Structural Determinacy Fundamentals</t>
         </is>
       </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr"/>
@@ -5014,6 +5881,11 @@
           <t>Stress and Strain Fundamentals</t>
         </is>
       </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr"/>
@@ -5034,6 +5906,11 @@
           <t>Tension, Compression, and Shear in Buildings</t>
         </is>
       </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr"/>
@@ -5054,6 +5931,11 @@
           <t>Bending and Deflection Fundamentals</t>
         </is>
       </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr"/>
@@ -5074,6 +5956,11 @@
           <t>Material Strength and Structural Behavior</t>
         </is>
       </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr"/>
@@ -5094,6 +5981,11 @@
           <t>Load-Bearing Wall Systems</t>
         </is>
       </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr"/>
@@ -5114,6 +6006,11 @@
           <t>Post-and-Beam Systems</t>
         </is>
       </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr"/>
@@ -5134,6 +6031,11 @@
           <t>Frame Structural Systems</t>
         </is>
       </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr"/>
@@ -5154,6 +6056,11 @@
           <t>Truss Systems</t>
         </is>
       </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr"/>
@@ -5174,6 +6081,11 @@
           <t>Arch and Vault Structures</t>
         </is>
       </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr"/>
@@ -5194,6 +6106,11 @@
           <t>Cable and Tensile Structures</t>
         </is>
       </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr"/>
@@ -5214,6 +6131,11 @@
           <t>Shell and Space-Frame Structures</t>
         </is>
       </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr"/>
@@ -5234,6 +6156,11 @@
           <t>Long-Span Structural Systems</t>
         </is>
       </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr"/>
@@ -5254,6 +6181,11 @@
           <t>Reinforced Concrete Structural Systems</t>
         </is>
       </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr"/>
@@ -5274,6 +6206,11 @@
           <t>Reinforced Concrete Beams and Slabs</t>
         </is>
       </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr"/>
@@ -5294,6 +6231,11 @@
           <t>Reinforced Concrete Columns</t>
         </is>
       </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr"/>
@@ -5314,6 +6256,11 @@
           <t>Reinforced Concrete Building Frames</t>
         </is>
       </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr"/>
@@ -5334,6 +6281,11 @@
           <t>Structural Steel Building Systems</t>
         </is>
       </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr"/>
@@ -5354,6 +6306,11 @@
           <t>Timber Structural Systems</t>
         </is>
       </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr"/>
@@ -5374,6 +6331,11 @@
           <t>Composite Structural Systems</t>
         </is>
       </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr"/>
@@ -5394,6 +6356,11 @@
           <t>Fundamentals of Seismic Design</t>
         </is>
       </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr"/>
@@ -5414,6 +6381,11 @@
           <t>Building Response to Earthquakes</t>
         </is>
       </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr"/>
@@ -5434,6 +6406,11 @@
           <t>Lateral Load-Resisting Systems</t>
         </is>
       </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr"/>
@@ -5454,6 +6431,11 @@
           <t>Architectural Configuration and Seismic Performance</t>
         </is>
       </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr"/>
@@ -5474,6 +6456,11 @@
           <t>Wind-Resistant Building Design</t>
         </is>
       </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr"/>
@@ -5494,6 +6481,11 @@
           <t>Disaster-Resilient Structural Planning</t>
         </is>
       </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -5522,6 +6514,11 @@
       <c r="F152" s="5" t="inlineStr">
         <is>
           <t>Origins and Development of Architecture</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
         </is>
       </c>
     </row>
@@ -5544,6 +6541,11 @@
           <t>Factors Influencing Architectural Styles</t>
         </is>
       </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr"/>
@@ -5564,6 +6566,11 @@
           <t>Prehistoric Architecture</t>
         </is>
       </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr"/>
@@ -5584,6 +6591,11 @@
           <t>Architectural Style Analysis and Identification</t>
         </is>
       </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr"/>
@@ -5604,6 +6616,11 @@
           <t>Egyptian Architecture</t>
         </is>
       </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr"/>
@@ -5624,6 +6641,11 @@
           <t>West Asiatic and Mesopotamian Architecture</t>
         </is>
       </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr"/>
@@ -5644,6 +6666,11 @@
           <t>Early Christian Architecture</t>
         </is>
       </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr"/>
@@ -5664,6 +6691,11 @@
           <t>Byzantine Architecture</t>
         </is>
       </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr"/>
@@ -5684,6 +6716,11 @@
           <t>Romanesque Architecture</t>
         </is>
       </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr"/>
@@ -5704,6 +6741,11 @@
           <t>Baroque and Rococo Architecture</t>
         </is>
       </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr"/>
@@ -5724,6 +6766,11 @@
           <t>Neoclassical Architecture</t>
         </is>
       </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr"/>
@@ -5744,6 +6791,11 @@
           <t>Nineteenth-Century Architecture</t>
         </is>
       </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr"/>
@@ -5764,6 +6816,11 @@
           <t>Twentieth-Century Architectural Movements</t>
         </is>
       </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr"/>
@@ -5784,6 +6841,11 @@
           <t>Contemporary Architecture</t>
         </is>
       </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr"/>
@@ -5804,6 +6866,11 @@
           <t>Architecture of South Asia</t>
         </is>
       </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr"/>
@@ -5824,6 +6891,11 @@
           <t>Chinese Architecture</t>
         </is>
       </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr"/>
@@ -5844,6 +6916,11 @@
           <t>Japanese Architecture</t>
         </is>
       </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr"/>
@@ -5864,6 +6941,11 @@
           <t>Southeast Asian Architecture</t>
         </is>
       </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr"/>
@@ -5884,6 +6966,11 @@
           <t>Pre-Colonial Philippine Architecture</t>
         </is>
       </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr"/>
@@ -5904,6 +6991,11 @@
           <t>Spanish Colonial Architecture in the Philippines</t>
         </is>
       </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr"/>
@@ -5924,6 +7016,11 @@
           <t>American Colonial Architecture in the Philippines</t>
         </is>
       </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr"/>
@@ -5944,6 +7041,11 @@
           <t>Postwar and Modern Philippine Architecture</t>
         </is>
       </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr"/>
@@ -5964,6 +7066,11 @@
           <t>Contemporary Philippine Architecture</t>
         </is>
       </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr"/>
@@ -5984,6 +7091,11 @@
           <t>Filipino Architects and Their Major Works</t>
         </is>
       </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr"/>
@@ -6004,6 +7116,11 @@
           <t>Major Architects and Their Design Philosophies</t>
         </is>
       </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr"/>
@@ -6024,6 +7141,11 @@
           <t>Landmark Works of Modern Architecture</t>
         </is>
       </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr"/>
@@ -6044,6 +7166,11 @@
           <t>Major Contemporary Architectural Movements</t>
         </is>
       </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
@@ -6072,6 +7199,11 @@
       <c r="F180" s="5" t="inlineStr">
         <is>
           <t>Reinforced Concrete Construction Principles</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -6094,6 +7226,11 @@
           <t>Concrete Formwork</t>
         </is>
       </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr"/>
@@ -6114,6 +7251,11 @@
           <t>Masonry Wall Systems</t>
         </is>
       </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr"/>
@@ -6134,6 +7276,11 @@
           <t>Concrete Finishes</t>
         </is>
       </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr"/>
@@ -6154,6 +7301,11 @@
           <t>Timber Framing Systems</t>
         </is>
       </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr"/>
@@ -6174,6 +7326,11 @@
           <t>Carpentry and Joinery</t>
         </is>
       </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr"/>
@@ -6194,6 +7351,11 @@
           <t>Wood Connections</t>
         </is>
       </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr"/>
@@ -6214,6 +7376,11 @@
           <t>Structural Steel Construction Systems</t>
         </is>
       </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr"/>
@@ -6234,6 +7401,11 @@
           <t>Light-Gauge Metal Construction</t>
         </is>
       </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr"/>
@@ -6254,6 +7426,11 @@
           <t>Sheet Metal and Tinsmithry</t>
         </is>
       </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr"/>
@@ -6274,6 +7451,11 @@
           <t>Metal Connections and Architectural Detailing</t>
         </is>
       </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr"/>
@@ -6294,6 +7476,11 @@
           <t>Wall and Cladding Systems</t>
         </is>
       </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr"/>
@@ -6314,6 +7501,11 @@
           <t>Glass and Glazing</t>
         </is>
       </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr"/>
@@ -6334,6 +7526,11 @@
           <t>Fenestration Systems</t>
         </is>
       </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr"/>
@@ -6354,6 +7551,11 @@
           <t>Thermal Insulation</t>
         </is>
       </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr"/>
@@ -6374,6 +7576,11 @@
           <t>Damp-Proofing</t>
         </is>
       </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr"/>
@@ -6394,6 +7601,11 @@
           <t>Building Envelope Performance</t>
         </is>
       </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr"/>
@@ -6414,6 +7626,11 @@
           <t>Wall Finishes</t>
         </is>
       </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr"/>
@@ -6434,6 +7651,11 @@
           <t>Ceiling Systems</t>
         </is>
       </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr"/>
@@ -6454,6 +7676,11 @@
           <t>Paints, Coatings, and Varnishes</t>
         </is>
       </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr"/>
@@ -6474,6 +7701,11 @@
           <t>Architectural Hardware</t>
         </is>
       </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr"/>
@@ -6494,6 +7726,11 @@
           <t>Doors and Windows</t>
         </is>
       </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr"/>
@@ -6514,6 +7751,11 @@
           <t>Interior Finish Selection</t>
         </is>
       </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr"/>
@@ -6534,6 +7776,11 @@
           <t>Material Specifications and Selection</t>
         </is>
       </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -6562,6 +7809,11 @@
       <c r="F205" s="5" t="inlineStr">
         <is>
           <t>Fundamentals of Urban and Regional Planning</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -6584,6 +7836,11 @@
           <t>General Planning Process</t>
         </is>
       </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr"/>
@@ -6604,6 +7861,11 @@
           <t>History of Urban Planning</t>
         </is>
       </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr"/>
@@ -6624,6 +7886,11 @@
           <t>Planning Theories and Models</t>
         </is>
       </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr"/>
@@ -6644,6 +7911,11 @@
           <t>Land Use Planning Principles</t>
         </is>
       </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr"/>
@@ -6664,6 +7936,11 @@
           <t>Urban Form and Spatial Structure</t>
         </is>
       </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr"/>
@@ -6684,6 +7961,11 @@
           <t>Urban Design Principles</t>
         </is>
       </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr"/>
@@ -6704,6 +7986,11 @@
           <t>Streetscape and Public Realm Design</t>
         </is>
       </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr"/>
@@ -6724,6 +8011,11 @@
           <t>Urbanization and Human Settlements</t>
         </is>
       </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr"/>
@@ -6744,6 +8036,11 @@
           <t>Principles of Housing and Human Settlements</t>
         </is>
       </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr"/>
@@ -6764,6 +8061,11 @@
           <t>Housing Typologies</t>
         </is>
       </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr"/>
@@ -6784,6 +8086,11 @@
           <t>Community Planning</t>
         </is>
       </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -6812,6 +8119,11 @@
       <c r="F218" s="5" t="inlineStr">
         <is>
           <t>Nature of Architecture as Art and Science</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
         </is>
       </c>
     </row>
@@ -6834,6 +8146,11 @@
           <t>Elements of Architecture</t>
         </is>
       </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr"/>
@@ -6854,6 +8171,11 @@
           <t>Principles of Architectural Composition</t>
         </is>
       </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr"/>
@@ -6874,6 +8196,11 @@
           <t>Form, Space, and Order</t>
         </is>
       </c>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr"/>
@@ -6894,6 +8221,11 @@
           <t>Architectural Design Processes</t>
         </is>
       </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr"/>
@@ -6914,6 +8246,11 @@
           <t>Visual Perception in Architecture</t>
         </is>
       </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr"/>
@@ -6934,6 +8271,11 @@
           <t>Psychology of Architectural Space</t>
         </is>
       </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr"/>
@@ -6954,6 +8296,11 @@
           <t>Proxemics and Territoriality</t>
         </is>
       </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr"/>
@@ -6974,6 +8321,11 @@
           <t>Human Behavior and Spatial Design</t>
         </is>
       </c>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr"/>
@@ -6994,6 +8346,11 @@
           <t>Tropical Architecture Principles</t>
         </is>
       </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr"/>
@@ -7014,6 +8371,11 @@
           <t>Tropical Architecture in the Philippines</t>
         </is>
       </c>
+      <c r="G228" s="5" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
@@ -7042,6 +8404,11 @@
       <c r="F230" s="5" t="inlineStr">
         <is>
           <t>Zoning and Locational Regulations</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7064,6 +8431,11 @@
           <t>Philippine Electrical Code for Architects</t>
         </is>
       </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr"/>
@@ -7084,6 +8456,11 @@
           <t>National Plumbing Code for Architects</t>
         </is>
       </c>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr"/>
@@ -7104,6 +8481,11 @@
           <t>Sanitation Code Provisions for Buildings</t>
         </is>
       </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr"/>
@@ -7124,6 +8506,11 @@
           <t>Housing and Subdivision Regulations</t>
         </is>
       </c>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
@@ -7152,6 +8539,11 @@
       <c r="F236" s="5" t="inlineStr">
         <is>
           <t>Site Zoning and Functional Organization</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -7174,6 +8566,11 @@
           <t>Pedestrian Circulation in Site Planning</t>
         </is>
       </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr"/>
@@ -7194,6 +8591,11 @@
           <t>Vehicular Circulation and Access</t>
         </is>
       </c>
+      <c r="G238" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr"/>
@@ -7214,6 +8616,11 @@
           <t>Service Access and Loading</t>
         </is>
       </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr"/>
@@ -7234,6 +8641,11 @@
           <t>Subdivision Planning</t>
         </is>
       </c>
+      <c r="G240" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
@@ -7262,6 +8674,11 @@
       <c r="F242" s="5" t="inlineStr">
         <is>
           <t>Architectural Heritage Conservation</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7284,6 +8701,11 @@
           <t>Architectural Preservation and Restoration</t>
         </is>
       </c>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr"/>
@@ -7304,6 +8726,11 @@
           <t>Adaptive Reuse of Historic Buildings</t>
         </is>
       </c>
+      <c r="G244" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr"/>
@@ -7324,6 +8751,11 @@
           <t>Philippine Heritage Conservation Principles</t>
         </is>
       </c>
+      <c r="G245" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -7352,6 +8784,11 @@
       <c r="F247" s="5" t="inlineStr">
         <is>
           <t>Landscape Design Principles</t>
+        </is>
+      </c>
+      <c r="G247" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -7374,6 +8811,11 @@
           <t>Hardscape and Softscape Planning</t>
         </is>
       </c>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr"/>
@@ -7394,6 +8836,11 @@
           <t>Planting Design Fundamentals</t>
         </is>
       </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr"/>
@@ -7414,6 +8861,11 @@
           <t>Open Space Planning</t>
         </is>
       </c>
+      <c r="G250" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
@@ -7442,6 +8894,11 @@
       <c r="F252" s="5" t="inlineStr">
         <is>
           <t>Development Controls and Building Regulations</t>
+        </is>
+      </c>
+      <c r="G252" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7464,6 +8921,11 @@
           <t>Easements and Rights-of-Way</t>
         </is>
       </c>
+      <c r="G253" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -7494,6 +8956,11 @@
           <t>Fire Code of the Philippines</t>
         </is>
       </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -7524,6 +8991,11 @@
           <t>Philippine Green Building Code</t>
         </is>
       </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -7554,6 +9026,11 @@
           <t>Site Grading Principles</t>
         </is>
       </c>
+      <c r="G259" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
@@ -7582,6 +9059,11 @@
       <c r="F261" s="5" t="inlineStr">
         <is>
           <t>Philippine Housing Policies and Programs</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -7675,7 +9157,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Interior Design</t>
+          <t>Architecture, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7695,7 +9177,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Architectural Engineering · Architecture · Interior Design · Landscape Architecture</t>
+          <t>Architecture, Architectural Engineering, Interior Design, Landscape Architecture</t>
         </is>
       </c>
     </row>
@@ -7715,7 +9197,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Architectural Engineering · Architecture</t>
+          <t>Architecture, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -7735,7 +9217,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Interior Design</t>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7755,7 +9237,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Interior Design</t>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7775,7 +9257,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Architectural Engineering · Architecture · Civil Engineering · Interior Design</t>
+          <t>Architecture, Architectural Engineering, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7795,7 +9277,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Architectural Engineering · Architecture · Civil Engineering · Electrical Engineering · Interior Design · Mechanical Engineering</t>
+          <t>Architecture, Architectural Engineering, Civil Engineering, Mechanical Engineering, Electrical Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7815,7 +9297,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Construction Management</t>
+          <t>Architecture, Civil Engineering, Construction Management</t>
         </is>
       </c>
     </row>
@@ -7835,7 +9317,7 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Construction Management · Industrial Engineering</t>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
         </is>
       </c>
     </row>
@@ -7855,7 +9337,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Architectural Engineering · Architecture · Civil Engineering</t>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -7875,7 +9357,7 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Construction Management</t>
+          <t>Architecture, Civil Engineering, Construction Management</t>
         </is>
       </c>
     </row>
@@ -7895,7 +9377,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Interior Design</t>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7915,7 +9397,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Architectural Engineering · Architecture · Civil Engineering</t>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -7935,7 +9417,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Interior Design · Landscape Architecture</t>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
         </is>
       </c>
     </row>
@@ -7955,7 +9437,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Environmental Planning · Landscape Architecture</t>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -7975,7 +9457,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Interior Design</t>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -7995,7 +9477,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Interior Design</t>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -8015,7 +9497,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Construction Management</t>
+          <t>Architecture, Civil Engineering, Construction Management</t>
         </is>
       </c>
     </row>
@@ -8035,7 +9517,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Civil Engineering · Construction Management · Industrial Engineering</t>
+          <t>Architecture, Civil Engineering, Construction Management, Industrial Engineering</t>
         </is>
       </c>
     </row>
@@ -8055,7 +9537,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Environmental Planning · Landscape Architecture</t>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -8075,7 +9557,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Environmental Planning · Landscape Architecture</t>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -8095,7 +9577,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Environmental Planning · Landscape Architecture</t>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -8115,7 +9597,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Architectural Engineering · Architecture · Civil Engineering</t>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -8135,7 +9617,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Interior Design · Landscape Architecture</t>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
         </is>
       </c>
     </row>
@@ -8155,7 +9637,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Environmental Planning · Landscape Architecture</t>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -8175,7 +9657,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Architecture · Environmental Planning · Landscape Architecture</t>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -8195,7 +9677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8205,6 +9687,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8257,6 +9740,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -8288,6 +9776,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr"/>
@@ -8315,6 +9808,11 @@
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -8342,6 +9840,11 @@
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -8369,6 +9872,11 @@
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8400,6 +9908,11 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -8427,6 +9940,11 @@
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -8458,6 +9976,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -8489,6 +10012,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8520,6 +10048,11 @@
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -8547,6 +10080,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -8574,6 +10112,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
@@ -8605,6 +10148,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8638,6 +10186,11 @@
       <c r="G20" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
         </is>
       </c>
     </row>
@@ -8667,6 +10220,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -8694,6 +10252,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -8721,6 +10284,11 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
@@ -8752,6 +10320,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -8779,6 +10352,11 @@
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
@@ -8806,6 +10384,11 @@
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -8837,6 +10420,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -8868,6 +10456,11 @@
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -8895,6 +10488,11 @@
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr"/>
@@ -8922,6 +10520,11 @@
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
@@ -8949,6 +10552,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -8980,6 +10588,11 @@
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr"/>
@@ -9007,6 +10620,11 @@
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -9034,6 +10652,11 @@
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
@@ -9061,6 +10684,11 @@
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
@@ -9088,6 +10716,11 @@
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
@@ -9115,6 +10748,11 @@
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -9146,6 +10784,11 @@
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -9173,6 +10816,11 @@
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -9200,6 +10848,11 @@
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
@@ -9227,6 +10880,11 @@
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -9258,6 +10916,11 @@
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -9285,6 +10948,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -9312,6 +10980,11 @@
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -9339,6 +11012,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
@@ -9366,6 +11044,11 @@
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr"/>
@@ -9393,6 +11076,11 @@
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr"/>
@@ -9420,6 +11108,11 @@
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -9451,6 +11144,11 @@
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -9478,6 +11176,11 @@
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -9505,6 +11208,11 @@
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -9532,6 +11240,11 @@
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr"/>
@@ -9563,6 +11276,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -9596,6 +11314,11 @@
       <c r="G60" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -9629,6 +11352,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr"/>
@@ -9660,6 +11388,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr"/>
@@ -9691,6 +11424,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr"/>
@@ -9718,6 +11456,11 @@
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr"/>
@@ -9745,6 +11488,11 @@
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -9776,6 +11524,11 @@
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr"/>
@@ -9803,6 +11556,11 @@
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr"/>
@@ -9830,6 +11588,11 @@
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9846,7 +11609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9856,6 +11619,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9908,6 +11672,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -9941,6 +11710,11 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
         </is>
       </c>
     </row>
@@ -9970,6 +11744,11 @@
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -9997,6 +11776,11 @@
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -10024,6 +11808,11 @@
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -10051,6 +11840,11 @@
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -10078,6 +11872,11 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -10105,6 +11904,11 @@
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -10132,6 +11936,11 @@
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -10165,6 +11974,11 @@
       <c r="G14" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
         </is>
       </c>
     </row>
@@ -10198,6 +12012,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -10225,6 +12044,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -10252,6 +12076,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
@@ -10279,6 +12108,11 @@
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -10306,6 +12140,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -10333,6 +12172,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -10360,6 +12204,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -10393,6 +12242,11 @@
       <c r="G23" s="20" t="inlineStr">
         <is>
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -10426,6 +12280,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -10457,6 +12316,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
@@ -10488,6 +12352,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -10519,6 +12388,11 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -10546,6 +12420,11 @@
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -10573,6 +12452,11 @@
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr"/>
@@ -10600,6 +12484,11 @@
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
@@ -10627,6 +12516,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -10654,6 +12548,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -10685,6 +12584,11 @@
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -10712,6 +12616,11 @@
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
@@ -10739,6 +12648,11 @@
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
@@ -10766,6 +12680,11 @@
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
@@ -10793,6 +12712,11 @@
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -10824,6 +12748,11 @@
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -10851,6 +12780,11 @@
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -10878,6 +12812,11 @@
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
@@ -10905,6 +12844,11 @@
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr"/>
@@ -10932,6 +12876,11 @@
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -10963,6 +12912,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -10990,6 +12944,11 @@
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -11017,6 +12976,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
@@ -11044,6 +13008,11 @@
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -11075,6 +13044,11 @@
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr"/>
@@ -11102,6 +13076,11 @@
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
@@ -11129,6 +13108,11 @@
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -11156,6 +13140,11 @@
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -11183,6 +13172,11 @@
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -11210,6 +13204,11 @@
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -11241,6 +13240,11 @@
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr"/>
@@ -11268,6 +13272,11 @@
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr"/>
@@ -11295,6 +13304,11 @@
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr"/>
@@ -11322,6 +13336,11 @@
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11338,7 +13357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11348,6 +13367,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11400,6 +13420,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -11433,6 +13458,11 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -11466,6 +13496,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -11497,6 +13532,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -11528,6 +13568,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -11561,6 +13606,11 @@
       <c r="G10" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
         </is>
       </c>
     </row>
@@ -11594,6 +13644,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -11625,6 +13680,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -11656,6 +13716,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -11687,6 +13752,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -11720,6 +13790,11 @@
       <c r="G16" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -11753,6 +13828,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
@@ -11784,6 +13864,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -11815,6 +13900,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -11842,6 +13932,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -11869,6 +13964,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -11896,6 +13996,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -11923,6 +14028,11 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
@@ -11950,6 +14060,11 @@
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -11981,6 +14096,11 @@
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -12008,6 +14128,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -12035,6 +14160,11 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -12062,6 +14192,11 @@
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -12095,6 +14230,11 @@
       <c r="G31" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
         </is>
       </c>
     </row>
@@ -12128,6 +14268,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -12155,6 +14300,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -12182,6 +14332,11 @@
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr"/>
@@ -12209,6 +14364,11 @@
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -12236,6 +14396,11 @@
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
@@ -12263,6 +14428,11 @@
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -12294,6 +14464,11 @@
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
@@ -12321,6 +14496,11 @@
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr"/>
@@ -12348,6 +14528,11 @@
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -12375,6 +14560,11 @@
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -12402,6 +14592,11 @@
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -12435,6 +14630,11 @@
       <c r="G45" s="20" t="inlineStr">
         <is>
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture</t>
         </is>
       </c>
     </row>
@@ -12464,6 +14664,11 @@
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -12491,6 +14696,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -12518,6 +14728,11 @@
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -12545,6 +14760,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Landscape Architecture, Environmental Planning</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12561,7 +14781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12571,6 +14791,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12623,6 +14844,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -12656,6 +14882,11 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -12689,6 +14920,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -12720,6 +14956,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -12751,6 +14992,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -12782,6 +15028,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -12813,6 +15064,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -12844,6 +15100,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -12871,6 +15132,11 @@
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -12898,6 +15164,11 @@
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -12925,6 +15196,11 @@
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -12952,6 +15228,11 @@
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -12979,6 +15260,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -13012,6 +15298,11 @@
       <c r="G18" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -13045,6 +15336,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -13072,6 +15368,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -13099,6 +15400,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -13126,6 +15432,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -13153,6 +15464,11 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -13186,6 +15502,11 @@
       <c r="G25" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -13215,6 +15536,11 @@
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -13242,6 +15568,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -13269,6 +15600,11 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -13302,6 +15638,11 @@
       <c r="G30" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -13331,6 +15672,11 @@
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
@@ -13358,6 +15704,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -13385,6 +15736,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -13412,6 +15768,11 @@
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -13445,6 +15806,11 @@
       <c r="G36" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -13478,6 +15844,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
@@ -13505,6 +15876,11 @@
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
@@ -13532,6 +15908,11 @@
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
@@ -13559,6 +15940,11 @@
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr"/>
@@ -13586,6 +15972,11 @@
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -13613,6 +16004,11 @@
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -13640,6 +16036,11 @@
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -13673,6 +16074,11 @@
       <c r="G45" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -13702,6 +16108,11 @@
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -13729,6 +16140,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -13756,6 +16172,11 @@
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -13783,6 +16204,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
@@ -13810,6 +16236,11 @@
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr"/>
@@ -13837,6 +16268,11 @@
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -13868,6 +16304,11 @@
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
@@ -13895,6 +16336,11 @@
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -13922,6 +16368,11 @@
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -13949,6 +16400,11 @@
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -13976,6 +16432,11 @@
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -13992,7 +16453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14002,6 +16463,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14054,6 +16516,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -14087,6 +16554,11 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -14120,6 +16592,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -14151,6 +16628,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -14178,6 +16660,11 @@
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -14205,6 +16692,11 @@
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -14232,6 +16724,11 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -14259,6 +16756,11 @@
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14290,6 +16792,11 @@
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -14317,6 +16824,11 @@
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -14344,6 +16856,11 @@
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -14371,6 +16888,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -14402,6 +16924,11 @@
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -14429,6 +16956,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -14456,6 +16988,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -14483,6 +17020,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -14510,6 +17052,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -14537,6 +17084,11 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
@@ -14564,6 +17116,11 @@
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -14591,6 +17148,11 @@
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -14622,6 +17184,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -14649,6 +17216,11 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -14676,6 +17248,11 @@
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -14703,6 +17280,11 @@
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -14734,6 +17316,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -14761,6 +17348,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -14788,6 +17380,11 @@
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -14821,6 +17418,11 @@
       <c r="G36" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -14854,6 +17456,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
@@ -14885,6 +17492,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
@@ -14916,6 +17528,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
@@ -14947,6 +17564,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr"/>
@@ -14978,6 +17600,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -15009,6 +17636,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr"/>
@@ -15040,6 +17672,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
@@ -15067,6 +17704,11 @@
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr"/>
@@ -15094,6 +17736,11 @@
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
@@ -15121,6 +17768,11 @@
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -15148,6 +17800,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -15175,6 +17832,11 @@
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -15202,6 +17864,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
@@ -15229,6 +17896,11 @@
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr"/>
@@ -15256,6 +17928,11 @@
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -15287,6 +17964,11 @@
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
@@ -15314,6 +17996,11 @@
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -15341,6 +18028,11 @@
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -15368,6 +18060,11 @@
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -15395,6 +18092,11 @@
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr"/>
@@ -15422,6 +18124,11 @@
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15438,7 +18145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15448,6 +18155,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15500,6 +18208,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -15533,6 +18246,11 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
         </is>
       </c>
     </row>
@@ -15566,6 +18284,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -15597,6 +18320,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -15624,6 +18352,11 @@
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -15651,6 +18384,11 @@
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -15678,6 +18416,11 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -15705,6 +18448,11 @@
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -15732,6 +18480,11 @@
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -15759,6 +18512,11 @@
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Civil Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -15792,6 +18550,11 @@
       <c r="G15" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
         </is>
       </c>
     </row>
@@ -15825,6 +18588,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -15852,6 +18620,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
@@ -15879,6 +18652,11 @@
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -15906,6 +18684,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -15933,6 +18716,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -15960,6 +18748,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -15993,6 +18786,11 @@
       <c r="G23" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
         </is>
       </c>
     </row>
@@ -16026,6 +18824,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -16053,6 +18856,11 @@
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
@@ -16080,6 +18888,11 @@
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -16107,6 +18920,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -16134,6 +18952,11 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -16161,6 +18984,11 @@
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -16188,6 +19016,11 @@
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Electrical Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -16221,6 +19054,11 @@
       <c r="G32" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -16250,6 +19088,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -16277,6 +19120,11 @@
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr"/>
@@ -16304,6 +19152,11 @@
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -16337,6 +19190,11 @@
       <c r="G37" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
         </is>
       </c>
     </row>
@@ -16366,6 +19224,11 @@
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
@@ -16393,6 +19256,11 @@
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
@@ -16420,6 +19288,11 @@
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr"/>
@@ -16447,6 +19320,11 @@
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
@@ -16474,6 +19352,11 @@
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -16507,6 +19390,11 @@
       <c r="G44" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -16536,6 +19424,11 @@
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
@@ -16563,6 +19456,11 @@
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -16590,6 +19488,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
@@ -16617,6 +19520,11 @@
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -16644,6 +19552,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
@@ -16671,6 +19584,11 @@
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Architectural Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16687,7 +19605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16697,6 +19615,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16749,6 +19668,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -16782,6 +19706,11 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -16815,6 +19744,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -16846,6 +19780,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -16877,6 +19816,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -16910,6 +19854,11 @@
       <c r="G10" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -16943,6 +19892,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -16974,6 +19928,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -17005,6 +19964,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -17036,6 +20000,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -17067,6 +20036,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -17100,6 +20074,11 @@
       <c r="G17" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -17133,6 +20112,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -17164,6 +20148,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -17195,6 +20184,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -17226,6 +20220,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -17257,6 +20256,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -17290,6 +20294,11 @@
       <c r="G24" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -17323,6 +20332,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
@@ -17354,6 +20368,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -17385,6 +20404,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -17418,6 +20442,11 @@
       <c r="G29" s="20" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
         </is>
       </c>
     </row>
@@ -17451,6 +20480,11 @@
           <t>same canonical note in another plan — do not duplicate · context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr"/>
@@ -17478,6 +20512,11 @@
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
@@ -17505,6 +20544,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -17532,6 +20576,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -17563,6 +20612,11 @@
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -17590,6 +20644,11 @@
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
@@ -17617,6 +20676,11 @@
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
@@ -17644,6 +20708,11 @@
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr"/>
@@ -17671,6 +20740,11 @@
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
@@ -17698,6 +20772,11 @@
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Architecture, Civil Engineering, Interior Design</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
